--- a/converted_files/837/837I-inst-claim.xlsx
+++ b/converted_files/837/837I-inst-claim.xlsx
@@ -1872,7 +1872,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6918d0577f059d7aab1b4efc</t>
+          <t>69e82c69836d7d05c9a056f5</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2575,7 +2575,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6918d0577f059d7aab1b4efc</t>
+          <t>69e82c69836d7d05c9a056f5</t>
         </is>
       </c>
       <c r="B3"/>

--- a/converted_files/837/837I-inst-claim.xlsx
+++ b/converted_files/837/837I-inst-claim.xlsx
@@ -1872,7 +1872,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6918d0577f059d7aab1b4efc</t>
+          <t>69efef06ad4799caa7f5e377</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2575,7 +2575,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6918d0577f059d7aab1b4efc</t>
+          <t>69efef06ad4799caa7f5e377</t>
         </is>
       </c>
       <c r="B3"/>

--- a/converted_files/837/837I-inst-claim.xlsx
+++ b/converted_files/837/837I-inst-claim.xlsx
@@ -1872,7 +1872,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>69e82c69836d7d05c9a056f5</t>
+          <t>6a04cb3c618f76c4f7b195a6</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2575,7 +2575,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>69e82c69836d7d05c9a056f5</t>
+          <t>6a04cb3c618f76c4f7b195a6</t>
         </is>
       </c>
       <c r="B3"/>

--- a/converted_files/837/837I-inst-claim.xlsx
+++ b/converted_files/837/837I-inst-claim.xlsx
@@ -1872,7 +1872,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3c618f76c4f7b195a6</t>
+          <t>6a04cc5c1ef26d534baf40b4</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2575,7 +2575,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3c618f76c4f7b195a6</t>
+          <t>6a04cc5c1ef26d534baf40b4</t>
         </is>
       </c>
       <c r="B3"/>

--- a/converted_files/837/837I-inst-claim.xlsx
+++ b/converted_files/837/837I-inst-claim.xlsx
@@ -1872,7 +1872,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5c1ef26d534baf40b4</t>
+          <t>6a0614def8d6a2fc74348efe</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2575,7 +2575,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5c1ef26d534baf40b4</t>
+          <t>6a0614def8d6a2fc74348efe</t>
         </is>
       </c>
       <c r="B3"/>

--- a/converted_files/837/837I-inst-claim.xlsx
+++ b/converted_files/837/837I-inst-claim.xlsx
@@ -1872,7 +1872,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a0614def8d6a2fc74348efe</t>
+          <t>6a32cb6497613a0e499095d1</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2575,7 +2575,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6a0614def8d6a2fc74348efe</t>
+          <t>6a32cb6497613a0e499095d1</t>
         </is>
       </c>
       <c r="B3"/>
